--- a/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 8,08</t>
+          <t>-5,26; 7,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 3,92</t>
+          <t>-9,09; 4,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 8,77</t>
+          <t>-3,11; 9,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 0,32</t>
+          <t>-10,89; 0,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 261,17</t>
+          <t>-59,55; 245,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 138,5</t>
+          <t>-82,17; 178,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-76,48; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,5</t>
+          <t>-2,42; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,92</t>
+          <t>-1,0; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,11</t>
+          <t>-0,67; 3,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,17</t>
+          <t>-1,9; 1,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,3; 57,4</t>
+          <t>-53,61; 52,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 200,46</t>
+          <t>-35,81; 197,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 295,1</t>
+          <t>-30,9; 248,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,94; 125,88</t>
+          <t>-70,82; 119,13</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,33</t>
+          <t>0,49; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,73</t>
+          <t>-0,36; 4,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,67</t>
+          <t>-0,46; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,11</t>
+          <t>-5,01; -0,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 114,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,78</t>
+          <t>-1,37; 1,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,26</t>
+          <t>-0,96; 2,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,59</t>
+          <t>-0,03; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,02</t>
+          <t>-2,29; 0,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 72,71</t>
+          <t>-35,77; 72,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 132,48</t>
+          <t>-29,36; 136,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 229,47</t>
+          <t>-4,7; 229,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,97; 5,37</t>
+          <t>-77,18; 9,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 7,62</t>
+          <t>-4,56; 8,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 4,21</t>
+          <t>-9,28; 3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 9,6</t>
+          <t>-3,42; 8,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 0,07</t>
+          <t>-11,12; -0,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 245,86</t>
+          <t>-56,46; 322,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,17; 178,36</t>
+          <t>-82,27; 119,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,48; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,36</t>
+          <t>-2,57; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,82</t>
+          <t>-0,72; 2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,0</t>
+          <t>-0,38; 3,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,23</t>
+          <t>-1,83; 1,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 52,65</t>
+          <t>-54,91; 48,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,81; 197,96</t>
+          <t>-30,18; 199,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 248,81</t>
+          <t>-22,32; 261,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,82; 119,13</t>
+          <t>-69,97; 121,81</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,72</t>
+          <t>0,46; 4,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,62</t>
+          <t>-0,19; 4,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,81</t>
+          <t>-0,46; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; -0,29</t>
+          <t>-4,65; -0,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,21</t>
+          <t>-100,0; 137,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,88</t>
+          <t>-1,41; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,31</t>
+          <t>-0,59; 2,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,56</t>
+          <t>-0,11; 2,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,08</t>
+          <t>-2,36; 0,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 72,33</t>
+          <t>-35,58; 72,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 136,37</t>
+          <t>-19,85; 143,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 229,02</t>
+          <t>-8,03; 252,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 9,4</t>
+          <t>-75,5; 24,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-4,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-84,57%</t>
+          <t>-85,89%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 8,27</t>
+          <t>-4,25; 8,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 3,55</t>
+          <t>-9,11; 3,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 8,45</t>
+          <t>-3,1; 8,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,12; -0,1</t>
+          <t>-11,97; 0,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,46; 322,28</t>
+          <t>-53,97; 261,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,27; 119,07</t>
+          <t>-81,76; 138,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,27%</t>
+          <t>-11,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,35</t>
+          <t>-2,65; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,77</t>
+          <t>-0,66; 2,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,11</t>
+          <t>-0,56; 3,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,19</t>
+          <t>-1,72; 1,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 48,31</t>
+          <t>-53,3; 57,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 199,03</t>
+          <t>-28,33; 200,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 261,44</t>
+          <t>-20,82; 295,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,97; 121,81</t>
+          <t>-67,43; 145,81</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-81,79%</t>
+          <t>-79,58%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,68</t>
+          <t>0,46; 4,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,69</t>
+          <t>-0,34; 4,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,84</t>
+          <t>-0,51; 2,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; -0,01</t>
+          <t>-4,45; 0,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,75</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-48,79%</t>
+          <t>-43,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,81</t>
+          <t>-1,41; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,37</t>
+          <t>-0,76; 2,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,65</t>
+          <t>-0,18; 2,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,11</t>
+          <t>-2,41; 0,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 72,06</t>
+          <t>-35,3; 72,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 143,21</t>
+          <t>-24,08; 132,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 252,36</t>
+          <t>-13,18; 229,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 24,1</t>
+          <t>-76,74; 21,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-32,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-85,89%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.735862858973472</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.304928304427493</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.127508489041964</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.511728391172999</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2969876070285258</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3285221689545383</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.7210214005836231</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.8588863092887441</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,25; 8,08</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,11; 3,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 8,77</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; 0,47</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-53,97; 261,17</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-81,76; 138,5</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.253397663460805</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.109630863770461</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.097425530153675</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.97071479410091</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5396903096896069</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8175690625808707</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.080125753054634</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.922180415334457</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.767713779818617</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.4742155415706012</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.611743259986458</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.384983825979105</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-11,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,65; 1,5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 2,92</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,56; 3,11</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,72; 1,48</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-53,3; 57,4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-28,33; 200,46</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,82; 295,1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-67,43; 145,81</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5749263672364585</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9108126054888036</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.232256468129133</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.2098459612857251</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1548622821884744</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.4187652204592096</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.6533264110601503</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1155593919072396</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>209,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>194,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-79,58%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.652761855627341</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.6590706280244084</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.555869117836843</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.723263294277153</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5330343956193615</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2833202476105361</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2081928815597115</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6743057462483578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 4,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 4,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,51; 2,67</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,45; 0,02</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.496699491299772</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.92448104948921</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.111787635776365</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.48118522904633</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5740260567524461</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.004595225587708</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.951007424800958</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.458149472855386</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +813,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-43,44%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.886538403660406</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.686597252969455</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8156940097748538</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.026865011374956</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.096327436764041</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.94137126372163</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.7957638765068278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,41; 1,78</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 2,26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 2,59</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 0,2</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-35,3; 72,71</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,08; 132,48</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-13,18; 229,47</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-76,74; 21,01</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4564706475853038</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.3417307956206467</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.5092113766382652</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.445586655113224</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.331817554935789</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.728212115055396</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.669717313173194</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.02125420450248242</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2594946161236927</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7239989285613871</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.189309266810171</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.9849901501829464</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.08188565731513872</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2966742782059406</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.7281006934068505</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4344018089625217</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.413084065652946</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.7590183826011087</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.1768790824133249</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.414569984806879</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3530021260037194</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.240817583032531</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1317998919663743</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7674214618497472</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.783483369278651</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.26096457151942</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.593970723103002</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.1970111493825557</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.727125597995174</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.324790638339943</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.294659853369024</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2101424882705354</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +997,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
